--- a/Ревьюирование программных модулей/Report/разделы/Таблица размеров файлов сборки ImageEditor и Общие характеристики сборки.xlsx
+++ b/Ревьюирование программных модулей/Report/разделы/Таблица размеров файлов сборки ImageEditor и Общие характеристики сборки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Практика Малленом Системс\Maintenance of information systems\Ревьюирование программных модулей\Report\разделы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1967691C-D68F-4F57-9762-8A7000AC219F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56671D88-BA5D-4BC3-81F8-6DC11D08D9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7812" yWindow="0" windowWidth="15324" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица размеров файлов сборки " sheetId="1" r:id="rId1"/>
@@ -109,13 +109,13 @@
     <t>Общий размер файлов</t>
   </si>
   <si>
-    <t>2,80 МБ (2937305 байт)</t>
-  </si>
-  <si>
     <t>Размер на диске</t>
   </si>
   <si>
-    <t>2,81 МБ (2953216 байт)</t>
+    <t>3,50 МБ (3680802 байт)</t>
+  </si>
+  <si>
+    <t>4,26 МБ (4472832 байт)</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -616,7 +616,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -624,12 +624,12 @@
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
